--- a/results/Int All Data 0.4/Rando_8_permute.xlsx
+++ b/results/Int All Data 0.4/Rando_8_permute.xlsx
@@ -440,37 +440,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8033114236151466</v>
+        <v>0.780757327272649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7989738159497584</v>
+        <v>0.7804095266381712</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8012508770343969</v>
+        <v>0.782096015358325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7992953593581185</v>
+        <v>0.7817284141926764</v>
       </c>
     </row>
     <row r="6">
@@ -480,237 +480,237 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7992953593581185</v>
+        <v>0.7817284141926764</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7976351278640823</v>
+        <v>0.7843795331379106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7966442404128842</v>
+        <v>0.7843795331379106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7949577516927302</v>
+        <v>0.7749824593120607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7949577516927302</v>
+        <v>0.7773120348489349</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7942884076498922</v>
+        <v>0.7740178290869802</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8009818480782723</v>
+        <v>0.7736700284525024</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8033901952934999</v>
+        <v>0.7730006844096644</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.80371173870186</v>
+        <v>0.7691684207354605</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.80371173870186</v>
+        <v>0.7652573853829036</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8027208512506618</v>
+        <v>0.7787294946129641</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7980354429507956</v>
+        <v>0.776052118441612</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7997219316709496</v>
+        <v>0.7734009994963778</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8078392885583061</v>
+        <v>0.7734009994963778</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8081608319666662</v>
+        <v>0.7724101120451796</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8107856936857828</v>
+        <v>0.7737488001308557</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8120981245453411</v>
+        <v>0.7711437389429099</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8120981245453411</v>
+        <v>0.7597386329885458</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8120981245453411</v>
+        <v>0.7550532246886796</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8114287805025031</v>
+        <v>0.7511421893361225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8124721824059367</v>
+        <v>0.7505516169716379</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8067958866548725</v>
+        <v>0.7464830382623742</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7940520926148323</v>
+        <v>0.7389364532083318</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7883495396376503</v>
+        <v>0.7389364532083318</v>
       </c>
     </row>
     <row r="30">
@@ -720,127 +720,127 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7850028194234602</v>
+        <v>0.7369021638536999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8075440023760637</v>
+        <v>0.7377617651743092</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8055359702475497</v>
+        <v>0.737440221765949</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.789708028254497</v>
+        <v>0.721106935781712</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7903773722973351</v>
+        <v>0.721106935781712</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.790725172931813</v>
+        <v>0.7236792830485931</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7950627805972013</v>
+        <v>0.7266519454021876</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6916097401395507</v>
+        <v>0.7444616622976364</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6918787690956753</v>
+        <v>0.7491208133713848</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6854543576234198</v>
+        <v>0.7587016877800592</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6854543576234198</v>
+        <v>0.7563458550170672</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6848112708066995</v>
+        <v>0.7503217586315249</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6874623897519339</v>
+        <v>0.7232600283233686</v>
       </c>
     </row>
     <row r="43">
@@ -850,1137 +850,1137 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6858284154840153</v>
+        <v>0.7219475974638102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6898444797410435</v>
+        <v>0.724198401322331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6969119780300194</v>
+        <v>0.7228597132366551</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7011118428698718</v>
+        <v>0.7228597132366551</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7031198749983858</v>
+        <v>0.7296319253433885</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7031198749983858</v>
+        <v>0.7380118544919227</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7218877654239682</v>
+        <v>0.7811585032520221</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.713612865179905</v>
+        <v>0.7736842331813858</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7205426206433451</v>
+        <v>0.7773787540300537</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7469423244962702</v>
+        <v>0.8071708054081277</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7482810125819462</v>
+        <v>0.8103535255706642</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.755348510870922</v>
+        <v>0.8048610304024242</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7643977840622942</v>
+        <v>0.7274413839710396</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7695424785960563</v>
+        <v>0.7457039304054374</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7695424785960563</v>
+        <v>0.7450341559162695</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7377092507220737</v>
+        <v>0.7439382395606005</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7903382016813234</v>
+        <v>0.7439382395606005</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7417068057869205</v>
+        <v>0.757410348790661</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7443579247321548</v>
+        <v>0.7412346061631305</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.749824162674277</v>
+        <v>0.7451193842895698</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7472255581812781</v>
+        <v>0.7402174614858146</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6894002591286905</v>
+        <v>0.7457887283324078</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6965529857909667</v>
+        <v>0.7484794483399837</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.690686432762131</v>
+        <v>0.7475608758721919</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6907914616666021</v>
+        <v>0.7565378340801576</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6897743169892863</v>
+        <v>0.7584670945303185</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6909292044921378</v>
+        <v>0.7599697826676481</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.688678400633617</v>
+        <v>0.7264836408872359</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6943546963846813</v>
+        <v>0.7188057697026047</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6873005419319291</v>
+        <v>0.7424686957906653</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6877271142447604</v>
+        <v>0.7225726055346788</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7008316223091724</v>
+        <v>0.7222510621263187</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7008316223091724</v>
+        <v>0.7406509209399226</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7043685998011338</v>
+        <v>0.7396862907148423</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6991976480412539</v>
+        <v>0.7366085994567767</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7002147927185699</v>
+        <v>0.7342527666937848</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6987646190334758</v>
+        <v>0.7223685739743539</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7262598087957404</v>
+        <v>0.7085288635786446</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7259382653873802</v>
+        <v>0.7076692622580354</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7261285226651515</v>
+        <v>0.6094526014023942</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7261285226651515</v>
+        <v>0.5689966726498706</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7251638924400712</v>
+        <v>0.562565804482668</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7251638924400712</v>
+        <v>0.5553343061420387</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7294752428793416</v>
+        <v>0.5608857724574612</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7178536224210884</v>
+        <v>0.5502360998118949</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7178536224210884</v>
+        <v>0.5520736751938085</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7145792171903047</v>
+        <v>0.5118803187024625</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7134966446708593</v>
+        <v>0.5233379391090622</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7154982201044262</v>
+        <v>0.5038021324311178</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7104322972490176</v>
+        <v>0.5034805890227577</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7283074419865959</v>
+        <v>0.503559360701111</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7024793708596444</v>
+        <v>0.5130024922842495</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7024793708596444</v>
+        <v>0.5109682029296176</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6943749273621819</v>
+        <v>0.5182195018014178</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7028925993362518</v>
+        <v>0.5063749101443287</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7420025224154926</v>
+        <v>0.5063749101443287</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7389971461408333</v>
+        <v>0.5124975787393948</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7410378921904122</v>
+        <v>0.5094724019335649</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7453625864659066</v>
+        <v>0.5141250963123662</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7359655126400564</v>
+        <v>0.5141250963123662</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7264832104409062</v>
+        <v>0.5107783760981761</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7209644580465484</v>
+        <v>0.5139675529556598</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.723694348670136</v>
+        <v>0.5142890963640199</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6803905869996599</v>
+        <v>0.5142890963640199</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6846756802128127</v>
+        <v>0.5132917522178747</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6843541368044526</v>
+        <v>0.4987826977793274</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6926815515007512</v>
+        <v>0.5490820732017029</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6959757572627057</v>
+        <v>0.5490820732017029</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6962973006710658</v>
+        <v>0.6174929083967166</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6976359887567418</v>
+        <v>0.6174929083967166</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6890985162515012</v>
+        <v>0.6177886250252886</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6890985162515012</v>
+        <v>0.5881799437837093</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6894204901061911</v>
+        <v>0.5831075642333536</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6903971728285059</v>
+        <v>0.5766306383088624</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.694419693780481</v>
+        <v>0.5881472298626446</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.694419693780481</v>
+        <v>0.5829762781027648</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7005285880929937</v>
+        <v>0.5862373394973248</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7005285880929937</v>
+        <v>0.5692084522441319</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6609852055596448</v>
+        <v>0.5742481178734229</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6609852055596448</v>
+        <v>0.5886181381474451</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6563398287684501</v>
+        <v>0.6258452889801436</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6566613721768102</v>
+        <v>0.6390160857793445</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6464770120137571</v>
+        <v>0.5234683643469914</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6458339251970369</v>
+        <v>0.5289871167413491</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6504732757396143</v>
+        <v>0.5287443450113423</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6091121183555228</v>
+        <v>0.5293874318280625</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.583020614074734</v>
+        <v>0.5293874318280625</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5730592251105171</v>
+        <v>0.5197475862722056</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5721010515803837</v>
+        <v>0.5193468407391625</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5721010515803837</v>
+        <v>0.5392037603791371</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.582246241127425</v>
+        <v>0.5392037603791371</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6031134183034388</v>
+        <v>0.5434557092248953</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5829082675826565</v>
+        <v>0.5468024294390854</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5853161843515541</v>
+        <v>0.5023562632093217</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5853161843515541</v>
+        <v>0.4988257424123073</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.569639329020261</v>
+        <v>0.5007550028624681</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5698295862980325</v>
+        <v>0.5011944885651932</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5506678374806837</v>
+        <v>0.4986221412983122</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5429047379227521</v>
+        <v>0.4963911379709621</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5635687444311006</v>
+        <v>0.5028284628331117</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5699996125983031</v>
+        <v>0.5028284628331117</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5699996125983031</v>
+        <v>0.5025069194247516</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5699996125983031</v>
+        <v>0.4951441349535333</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5449192267462131</v>
+        <v>0.4951441349535333</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5415591626957993</v>
+        <v>0.4872303791801719</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5262757353099429</v>
+        <v>0.4954265077458817</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5408571047318965</v>
+        <v>0.5144505137376947</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5421957928175726</v>
+        <v>0.5144505137376947</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5579320497423779</v>
+        <v>0.51911612150639</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5816612645652277</v>
+        <v>0.5010369452084866</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5808998050078126</v>
+        <v>0.5010369452084866</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4997649763039295</v>
+        <v>0.4998097427222287</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4997649763039295</v>
+        <v>0.4998097427222287</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4961621405235088</v>
+        <v>0.4998097427222287</v>
       </c>
     </row>
   </sheetData>
